--- a/RoboticEnterpriseFramework/Data/Input/Book1.xlsx
+++ b/RoboticEnterpriseFramework/Data/Input/Book1.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Documents\UiPath\RoboticEnterpriseFramework\Data\Input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automation\Sem 7 RPA\RoboticEnterpriseFramework\Data\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C76B79C4-CDA8-4E4F-B58D-1975995F2393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B8B2C2-6B19-48F6-AA4C-654382A0179B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{F7B6DD1E-441C-4727-AF54-09F425C09443}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D4E4D6FD-A357-44B5-8CA5-82EC51C39968}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -405,11 +405,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{424D1B26-55EA-4669-8D01-60B9E6DE4F43}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A046599C-84DF-40CD-A1A0-A4DB20AFABE1}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -426,7 +426,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -443,7 +443,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -460,7 +460,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -477,7 +477,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -494,7 +494,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
